--- a/spreadsheet/Lab3B_Risk_Quantification_Workbook.xlsx
+++ b/spreadsheet/Lab3B_Risk_Quantification_Workbook.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Lab 3B: Advanced Cybersecurity Risk Quantification - SecureBank Financial</t>
   </si>
   <si>
-    <t xml:space="preserve">Student: Chioma Ameh | Registration number: C11/26/CGRCE/17567 | Course: GRC102 | Date: 29 October 2026 (WAT)</t>
+    <t xml:space="preserve">Student: Chioma Ameh | Registration number: C11/26/CGRCE/17567 | Course: GRC103 | Date: 29 October 2026 (WAT)</t>
   </si>
   <si>
     <t xml:space="preserve">Colour legend</t>
@@ -1434,11 +1434,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="6135922"/>
-        <c:axId val="18552686"/>
+        <c:axId val="98306127"/>
+        <c:axId val="46119426"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6135922"/>
+        <c:axId val="98306127"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1504,7 +1504,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18552686"/>
+        <c:crossAx val="46119426"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1512,7 +1512,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18552686"/>
+        <c:axId val="46119426"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1588,7 +1588,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6135922"/>
+        <c:crossAx val="98306127"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2191,11 +2191,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="86421675"/>
-        <c:axId val="65379909"/>
+        <c:axId val="65980722"/>
+        <c:axId val="70638383"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86421675"/>
+        <c:axId val="65980722"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="400000"/>
@@ -2273,12 +2273,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65379909"/>
+        <c:crossAx val="70638383"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="65379909"/>
+        <c:axId val="70638383"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2356,7 +2356,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86421675"/>
+        <c:crossAx val="65980722"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2637,11 +2637,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="76320105"/>
-        <c:axId val="96905764"/>
+        <c:axId val="10843637"/>
+        <c:axId val="74377791"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76320105"/>
+        <c:axId val="10843637"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2707,7 +2707,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96905764"/>
+        <c:crossAx val="74377791"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2715,7 +2715,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96905764"/>
+        <c:axId val="74377791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2791,7 +2791,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76320105"/>
+        <c:crossAx val="10843637"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3072,11 +3072,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5430649"/>
-        <c:axId val="44133283"/>
+        <c:axId val="32634475"/>
+        <c:axId val="81025112"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5430649"/>
+        <c:axId val="32634475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3142,7 +3142,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44133283"/>
+        <c:crossAx val="81025112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3150,7 +3150,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44133283"/>
+        <c:axId val="81025112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3226,7 +3226,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5430649"/>
+        <c:crossAx val="32634475"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3507,11 +3507,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="64701881"/>
-        <c:axId val="80403358"/>
+        <c:axId val="86870299"/>
+        <c:axId val="63052490"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64701881"/>
+        <c:axId val="86870299"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3577,7 +3577,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80403358"/>
+        <c:crossAx val="63052490"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3585,7 +3585,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80403358"/>
+        <c:axId val="63052490"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3661,7 +3661,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64701881"/>
+        <c:crossAx val="86870299"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4065,11 +4065,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="66783246"/>
-        <c:axId val="53842438"/>
+        <c:axId val="58174053"/>
+        <c:axId val="79594421"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="66783246"/>
+        <c:axId val="58174053"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4135,7 +4135,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53842438"/>
+        <c:crossAx val="79594421"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4143,7 +4143,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53842438"/>
+        <c:axId val="79594421"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4219,7 +4219,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66783246"/>
+        <c:crossAx val="58174053"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4473,11 +4473,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="75509521"/>
-        <c:axId val="98458927"/>
+        <c:axId val="10457717"/>
+        <c:axId val="74256410"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="75509521"/>
+        <c:axId val="10457717"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4543,7 +4543,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98458927"/>
+        <c:crossAx val="74256410"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4551,7 +4551,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98458927"/>
+        <c:axId val="74256410"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4627,7 +4627,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75509521"/>
+        <c:crossAx val="10457717"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5186,11 +5186,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="42133223"/>
-        <c:axId val="3573555"/>
+        <c:axId val="41560619"/>
+        <c:axId val="5895172"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42133223"/>
+        <c:axId val="41560619"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -5256,7 +5256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3573555"/>
+        <c:crossAx val="5895172"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5264,7 +5264,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3573555"/>
+        <c:axId val="5895172"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="365"/>
@@ -5342,7 +5342,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42133223"/>
+        <c:crossAx val="41560619"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="30"/>
